--- a/sources/ling_step7.xlsx
+++ b/sources/ling_step7.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA150"/>
+  <dimension ref="A1:AB150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="280" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>874ba746-d7f5-4b19-9cf5-709a5bbb8de3</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>bb802c01-578a-4668-b589-3182cb1480f2</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>76accf4e-4c94-4698-aec5-96fe4410b827</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>cf24aa73-e196-4753-8f75-2a8677c4a59e</t>
         </is>
@@ -783,12 +789,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>7b8461d8-84a3-466b-aaa6-9141b75dd3f5</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>01d44127-7e8b-46d0-8d3c-408e0dcf5438</t>
         </is>
@@ -797,22 +803,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f+2~1 [~5]</t>
+          <t>f+2~1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f+2~1 [~5]</t>
+          <t>f+2~1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Human Hurdle [Tag]</t>
+          <t>Human Hurdle</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Human Hurdle [Tag]</t>
+          <t>Human Hurdle</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -862,10 +868,15 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>9736f1b9-bd3e-40b0-ace1-39836dcddbb5</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>c6fa184d-3605-4d0a-bc03-8bed3ee1e1a2</t>
         </is>
@@ -932,12 +943,12 @@
           <t>Requires about a third screen distance.</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>b9efd079-ac67-44e9-8ca8-ec04e15cac18</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>3403bf10-5918-4ca0-af7f-c089b6c78e82</t>
         </is>
@@ -1009,12 +1020,12 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>99d4757d-183e-42be-b50c-3d5aeeb50259</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>be7d3077-c90b-42e5-939f-e8825a2ce1b0</t>
         </is>
@@ -1076,12 +1087,12 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1090,27 +1101,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2+4 [~5]; 2+5 [~5]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arm Flip [Tag]</t>
+          <t>Arm Flip</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arm Flip [Tag]</t>
+          <t>Arm Flip</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1138,12 +1149,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1200,12 +1216,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1262,12 +1278,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1399,20 +1415,25 @@
       </c>
       <c r="X15" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr">
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1494,12 +1515,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>3d4e9688-0183-4bc6-a429-08ca94693a64</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0ecdc0e5-882b-4668-ab00-82a75cb4b99a</t>
         </is>
@@ -1581,12 +1602,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>8faa3815-3232-42c4-9d9c-a12d27877788</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>c301e47b-3422-48f1-b63a-8545ec007e09</t>
         </is>
@@ -1668,12 +1689,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>674f6ed0-a19e-4d6e-9b1a-8f6ce8767295</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>e64a4f85-2e0c-473e-a18a-f687dd63e572</t>
         </is>
@@ -1755,12 +1776,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>f5249c34-48a5-44d5-88e5-b856cf2ac33f</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>b9b2e290-db35-4498-88bd-cf49fba834f0</t>
         </is>
@@ -1842,12 +1863,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>654c590b-31b1-4e48-a8c7-1490f53611b0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>0576361d-32cb-4b30-8cff-8010fec75244</t>
         </is>
@@ -1929,12 +1950,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>326153e5-da5e-4e54-94cb-167f4e8438b9</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>05485f5b-c8d6-4703-b70d-a8cff30dcbed</t>
         </is>
@@ -2016,12 +2037,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>159ec1aa-69d1-4668-bcbe-997e418433fe</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>f3275c6c-946d-4f0b-bd70-6e480eca1fa9</t>
         </is>
@@ -2103,12 +2124,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>37b4723a-be31-4639-a5cd-059cf60d8091</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>aa40b9df-672f-4d85-ba90-ccdcc6b4063e</t>
         </is>
@@ -2190,12 +2211,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>b82887e9-a61d-4584-977d-ba57317e349d</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>a923518b-fe67-4965-bd42-d7ac2b636e3f</t>
         </is>
@@ -2277,12 +2298,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>bf84e8e5-f665-4138-bcb9-a26e3ef54bc7</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>5d332e14-a532-4cad-ad10-7cf71fc42b78</t>
         </is>
@@ -2364,12 +2385,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>38943d9f-55df-44bf-b43f-136c11d2677b</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>49bf1b20-3a34-418e-ab87-3f057c08f96a</t>
         </is>
@@ -2451,12 +2472,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>6abae15b-27f1-4104-8dfb-19656b0e4b80</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>5c77cfd5-db2e-486b-bf78-a5bfc930ec13</t>
         </is>
@@ -2538,12 +2559,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>69596f0f-8122-4867-a04d-918031b06b91</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>6e1dab43-d1a7-4938-93d9-418f8b9ac1e6</t>
         </is>
@@ -2625,12 +2646,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>1c16fcd8-3238-49f3-9cdc-29e5bdc5b9c3</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>d9a78570-4a7c-41a7-8221-23259ed7be12</t>
         </is>
@@ -2712,12 +2733,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>76e2df0e-a813-4660-908c-246d2b1d82fa</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>29b6b46f-815f-40fc-9351-8ef6498625c5</t>
         </is>
@@ -2799,12 +2820,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>518b7734-def4-4151-9778-6548a151545d</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>f1b2e14c-9234-44b9-b413-038443d1da0a</t>
         </is>
@@ -2886,12 +2907,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>5cdaf7f4-4a8b-4b30-b5c4-970f9f29a30d</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>58f45484-261f-4125-ab1b-f4704ca65a66</t>
         </is>
@@ -2973,12 +2994,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>493aab24-4dde-40c6-90c3-62c08b432bc3</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>a4b12e60-938d-4e77-8a5e-24c3f32a1e61</t>
         </is>
@@ -3060,12 +3081,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>7705f0ff-d1de-4875-a9f5-fcccd7e7d926</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>fe81c514-10df-452a-a6d6-d2807ee19444</t>
         </is>
@@ -3147,12 +3168,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>642e86ae-e1e5-4792-8202-8a35dc212a6c</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>ec1cda50-8fad-450c-bb74-3afe6a25812b</t>
         </is>
@@ -3234,12 +3255,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>13c8e9b0-e658-4dcc-967d-b7fa71d1effa</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>6e97e6f3-dbf1-4dde-a186-7cd7c3ddbfc5</t>
         </is>
@@ -3321,12 +3342,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>f9181a42-4111-43d9-bc55-9f4dcc0ff581</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>06a0142c-97ab-4a3e-9581-f40017c3a18b</t>
         </is>
@@ -3408,12 +3429,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>36e18bfa-d9b7-488f-924a-23d32baac0c5</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>88a32670-cb5c-4e71-b701-71c57d82b518</t>
         </is>
@@ -3495,12 +3516,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>9a35c142-35fa-42ef-9a4b-5d091de3ec50</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>ae7364bc-4c27-43f5-bda5-61c252199594</t>
         </is>
@@ -3632,20 +3653,25 @@
       </c>
       <c r="X42" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y42" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
+      <c r="Z42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z42" s="1" t="inlineStr">
+      <c r="AA42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA42" s="1" t="inlineStr">
+      <c r="AB42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3737,12 +3763,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>0d5bcd50-3254-4d6f-b4c5-f468b127b2a3</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>4f39db8a-736d-4d36-b385-b0dddf727818</t>
         </is>
@@ -3834,12 +3860,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>18057ba1-27d5-432d-a37f-ce626c5d96df</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>6208d182-4079-4a5c-9189-6dec7615fd12</t>
         </is>
@@ -3936,12 +3962,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>a1386b61-24f6-4d3b-88d3-4e54daef5e51</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>08772236-a4a3-40c3-bbcd-893933eb996a</t>
         </is>
@@ -4033,12 +4059,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>7b3b5f6a-fb1c-4ac5-a4d7-a16b94eeed0c</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>a9f8dbb7-6556-4515-9072-e71b15fa96ba</t>
         </is>
@@ -4135,12 +4161,12 @@
           <t>Damage is 37 on a clean hit. On a counter hit Ling will do an automatic 1+3+4 taunt.</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>ada60b9c-5416-4a57-afff-308a55c3176b</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>e91952d3-8882-41ac-ab77-9b7c11730a3b</t>
         </is>
@@ -4237,12 +4263,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>872799b9-49ce-435c-b8ef-ea13476ed59c</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>ddbfb051-516e-4934-8f96-c810a5e3e832</t>
         </is>
@@ -4334,12 +4360,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>0a1984b5-fe08-48b1-9bec-e091c9ab2b74</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>12612140-1769-4c58-aac3-b351caf4ad7a</t>
         </is>
@@ -4446,12 +4472,12 @@
           <t>Has to hit for Ling to go in RDS.</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>eb99dbf4-4081-4b01-9fbd-b152719bdd1d</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>cbf5c0d6-565b-492c-9e86-86f5e380a068</t>
         </is>
@@ -4548,12 +4574,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>1f252366-8668-4af0-b195-995f0ed7ed24</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>9166b9cd-c3c3-458a-aad8-799c49433c56</t>
         </is>
@@ -4650,12 +4676,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>a45a8361-3b4a-4e67-bc45-da8b314e5043</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>8bf0bc82-b4fe-4604-8c8c-aaef590ad31d</t>
         </is>
@@ -4752,12 +4778,12 @@
           <t>mMM</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>eef6efe3-7a0b-4e48-8b25-1fdaf76cd199</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>bd70090f-b411-45ad-8797-1dc0d32ebf21</t>
         </is>
@@ -4809,12 +4835,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>4579fe1a-4ded-4ab1-8378-2eec09ff10b8</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>b99e421d-52d3-4689-b7d4-dbe0900af623</t>
         </is>
@@ -4911,12 +4937,12 @@
           <t>RC GB</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>c578a7b3-221f-4fe4-a117-dd1d49969717</t>
         </is>
@@ -5003,17 +5029,17 @@
           <t>mmm</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>aadbdd07-dac3-4f6e-9230-207fed9671ef</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>20d0c7b5-efe5-4e46-86f0-179e7ba92fb6</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -5100,17 +5126,17 @@
           <t>mmmm</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>1fe5e046-832f-40fb-bc3f-b47d5d1f9f82</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>61f591c1-a9cd-42fd-bc47-bb38e37d22e8</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -5202,17 +5228,17 @@
           <t>mm-</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>b929cc95-3142-4aba-8191-88bca5e84bf1</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>882e63b0-f559-4ef6-82b3-112a95589e60</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -5314,12 +5340,12 @@
           <t>Bounce will occur only when the last hit is a counter hit.</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>d1404f6b-934d-4968-939b-d8bca00aa895</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>118c04cc-9a3e-4492-b06b-69c10b46a042</t>
         </is>
@@ -5416,12 +5442,12 @@
           <t>CF KNDc</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>b0b13203-5198-40bb-af7c-078bdfeb8823</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>6a69aa0c-6e48-42b8-b188-a6084c11cfb9</t>
         </is>
@@ -5518,12 +5544,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>3a375440-f7c9-4294-9658-ce43e25f44a2</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>51f8c1c6-8fc6-4340-9572-9c8d0987ef71</t>
         </is>
@@ -5615,12 +5641,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>c230105d-5660-44a1-8e56-3200c351bcea</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>d87766ec-0585-4885-82e4-030adb204e93</t>
         </is>
@@ -5629,22 +5655,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WS+2 [~5]</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WS+2 [~5]</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun Flower [Tag]</t>
+          <t>Sun Flower</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sun Flower [Tag]</t>
+          <t>Sun Flower</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5729,10 +5755,15 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
           <t>d4d02dff-7fbd-421d-8cc8-c8fe331eee39</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>5ba12b9a-3d74-4e93-ba59-097c6a0a01d4</t>
         </is>
@@ -5829,12 +5860,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>3e13f208-6740-4bd0-b40f-cb937d7c837a</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>9f11293a-e276-4d5d-a06e-42bfb2cfbbb2</t>
         </is>
@@ -5931,12 +5962,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>321a983c-005f-47c0-aae9-9e92eb3084a6</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>0b85571b-13f9-40dd-b439-05dd5d183abe</t>
         </is>
@@ -6033,12 +6064,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>c86a461d-9853-409e-8dbf-c140f78957bc</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>29fe6146-6448-4dc1-b260-e1da0f2682fb</t>
         </is>
@@ -6135,12 +6166,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>a2d0c94a-e4f1-4b84-867d-a8aacd632dde</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>71535751-0aff-41bc-b353-d8de0f10a87c</t>
         </is>
@@ -6149,22 +6180,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>df+2,1 [~5]</t>
+          <t>df+2,1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>df+2,1 [~5]</t>
+          <t>df+2,1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cross Lifting Palms [Tag]</t>
+          <t>Cross Lifting Palms</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cross Lifting Palms [Tag]</t>
+          <t>Cross Lifting Palms</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6239,10 +6270,15 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>6ca8b195-fd70-49e9-95ff-f068baffeef4</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>5dd79b04-bd05-487e-b258-4b23cbf1948f</t>
         </is>
@@ -6334,12 +6370,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>a87e6188-7f43-46a4-ab07-74e7a6df6d75</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>62fb2034-0e33-454a-9879-4446c986e9d7</t>
         </is>
@@ -6431,12 +6467,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>ba40070f-3541-4774-b6c2-3e6514a34549</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>2f59aa03-4e29-4e9e-9560-3826ac149e32</t>
         </is>
@@ -6533,12 +6569,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>c7ad3516-8d27-4ca8-b1c6-c74ee15c88c8</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>cf476e8d-471d-4590-b67d-27468570b504</t>
         </is>
@@ -6635,12 +6671,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>c01958d7-8362-449b-af6c-027346aabe6a</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>58a60921-36a8-4076-a001-e02f71d9264c</t>
         </is>
@@ -6649,22 +6685,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D+3,2,1,4 [~5]</t>
+          <t>D+3,2,1,4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D+3,2,1,4 [~5]</t>
+          <t>D+3,2,1,4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fire Dance [Tag]</t>
+          <t>Fire Dance</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fire Dance [Tag]</t>
+          <t>Fire Dance</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6739,10 +6775,15 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>fcaee446-6310-493e-a29b-7980137a4e3d</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>32c666d4-5778-4d06-865d-1e3dba39b4b0</t>
         </is>
@@ -6799,12 +6840,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>d09dd708-e5fd-49ca-921c-de3f19c95bdb</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>b426aeb9-b274-476a-ba58-d34a83e4bd86</t>
         </is>
@@ -6861,12 +6902,12 @@
           <t>Depending on your opponents position before the move Ling can end up in RDS.</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>fb27b361-92bd-42ac-894f-527ba7204cc5</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>7bb439b3-adaf-442e-9b88-4eb1bdc6c4e8</t>
         </is>
@@ -6963,12 +7004,12 @@
           <t>Depending on your opponents position before the move Ling can end up in RDS.</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>75cb1604-b604-46ef-8091-2243270682f9</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>5a8a5d0a-e454-47f0-a5e5-2039447cd13b</t>
         </is>
@@ -7060,12 +7101,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>c7ccb049-feaa-4dbb-960b-d898c19e8cc7</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>cca3e22f-9227-4dfe-b4fa-d24c56031928</t>
         </is>
@@ -7162,12 +7203,12 @@
           <t>KS SLDc</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>4f70efc9-f29d-499b-9b59-0bfcb8aec97b</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>2980281e-5707-48f4-b8e4-563db7ddb16e</t>
         </is>
@@ -7259,12 +7300,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>059b4353-a8cd-44d2-b4e7-239c136e63c4</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>6908745c-786b-41a4-960f-f5f3f0ee5d05</t>
         </is>
@@ -7356,12 +7397,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>77e41785-f559-4e94-935a-f393bfbd4411</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>83f5e942-21b7-4034-b5cc-72dabb3f9bb5</t>
         </is>
@@ -7458,12 +7499,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>dd5f73a9-6cab-4ba4-91a2-5bba6df2ac16</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>113a7f27-ae61-41a3-9373-36866580e20f</t>
         </is>
@@ -7520,12 +7561,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>d288a6b0-c084-494a-b866-6808c8f0b42b</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>b3d5cc22-7a23-424a-a6a0-ee5e8a86234a</t>
         </is>
@@ -7622,12 +7663,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>980d698e-01ea-48fb-b9e2-41fd6d42b795</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>c4d103c1-775e-4596-b5a2-58bbf692c078</t>
         </is>
@@ -7729,12 +7770,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>575f73c7-dbfa-4d31-8a40-4db2663c3a4d</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>66a76604-e344-4e65-8239-d0cabdc1a81f</t>
         </is>
@@ -7786,12 +7827,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>a4ae5fdb-c240-4fff-ba78-84ecd64e87b0</t>
         </is>
@@ -7883,17 +7924,17 @@
           <t>Damage increases to 30 then 35 as you Hypnotist Walk longer. Clean Hit damage will be 37,45 or 52.</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>4fb4d6e5-1428-47b8-84f7-b084a82d6f57</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>6c08bafe-f024-4808-b991-d6e90f7678ab</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
@@ -7945,17 +7986,17 @@
           <t>--</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>cde3cbb6-39e4-4bbd-8d1e-59d63f6766a9</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>97d5cd5d-2c92-4e6f-9259-be9897218dd1</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
@@ -8012,12 +8053,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>9cd78cfe-f850-44ec-8cbc-c1744ce20f54</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>9c49960f-f109-49bd-931b-0ac227f9a527</t>
         </is>
@@ -8074,12 +8115,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>3f6ba135-24e6-44ae-89c1-09dbdf045c6a</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>666f30a5-68a7-46f5-9686-5bf86fc4681e</t>
         </is>
@@ -8136,12 +8177,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>def84375-5011-4b11-84a0-885a34b25d85</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>c05e0674-0400-4165-9779-3e1a957236ba</t>
         </is>
@@ -8193,12 +8234,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>55f10e0e-b8fe-4478-8d4c-2fe839b19882</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>0f9d5da1-c35e-4d47-a0e5-ab212de8decf</t>
         </is>
@@ -8250,12 +8291,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>0f3dc3b0-1a09-42da-8a39-ca793941d837</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>1a5f0a2d-10a3-497b-9fcd-29520e5d3b81</t>
         </is>
@@ -8312,12 +8353,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>66d0bc20-2aec-47e1-a748-5b027c60d425</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>ce17d917-2b59-4a46-b0e4-7550d494f83a</t>
         </is>
@@ -8369,12 +8410,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>4f00b275-65c1-4e31-9c5b-02f3961f09dc</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>b4faf1a5-69a3-42f4-aedb-dbec07df51de</t>
         </is>
@@ -8466,12 +8507,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>0a724735-c333-4d7c-9b41-4bda114587c0</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>18706352-d2c1-4871-9334-8733a8ca4c58</t>
         </is>
@@ -8603,20 +8644,25 @@
       </c>
       <c r="X98" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y98" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y98" s="1" t="inlineStr">
+      <c r="Z98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z98" s="1" t="inlineStr">
+      <c r="AA98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA98" s="1" t="inlineStr">
+      <c r="AB98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8633,12 +8679,12 @@
           <t>Moves starting from Rain Dance Stance only - RDS</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>1463bdfa-6bdd-49d2-a3ac-280786b102dd</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>e386e57a-42fe-4297-8e0a-8db74be4ac98</t>
         </is>
@@ -8695,12 +8741,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>e90f1b2c-7bb0-4304-acf8-33dbc4a1634a</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>fa074052-d35d-4fa9-a46b-d4ad62900392</t>
         </is>
@@ -8757,12 +8803,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>40a1fbca-708f-4ab1-be5c-c60615ba0680</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>30e4a770-a0c0-4eda-b753-55a3bb608e8b</t>
         </is>
@@ -8771,22 +8817,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2,1,4 [~5]</t>
+          <t>2,1,4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2,1,4 [~5]</t>
+          <t>2,1,4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Dark &amp; Stormy [Tag]</t>
+          <t>Dark &amp; Stormy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dark &amp; Stormy [Tag]</t>
+          <t>Dark &amp; Stormy</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8866,10 +8912,15 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
           <t>9629caf3-6f10-4e33-a2d4-d73deedf7469</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>f6a9b652-ae23-4cef-8ee9-a3d3598a2405</t>
         </is>
@@ -8966,12 +9017,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>ba040e65-ad5e-4c64-a392-d40def463053</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>a0fb96a0-a340-4e63-9779-5fd48da4a1d8</t>
         </is>
@@ -9073,12 +9124,12 @@
           <t>FCDc</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>fbbbf1af-b438-4a15-91dd-a6c778a458e0</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>13025283-ecef-4950-b35f-93ace7ce4239</t>
         </is>
@@ -9175,12 +9226,12 @@
           <t>FCDc</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>1d476db7-0fef-4df3-a76a-9ebc7782df53</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>8a7c66bd-7aff-447b-bf87-05c78692484b</t>
         </is>
@@ -9272,12 +9323,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>5936552e-0d20-43e9-a341-81e555eede34</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>625a8401-986c-4710-94eb-d3e72202ab8e</t>
         </is>
@@ -9334,12 +9385,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>83d45d20-abe6-4ff5-bd03-2cf9f2d0b03d</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>9af711df-7250-47e6-8b78-57bcd1416cab</t>
         </is>
@@ -9396,12 +9447,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>72ceb8fa-8c13-414e-abde-e93840b782c9</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>bd8643e7-8f94-455b-8c84-3e50e022e63e</t>
         </is>
@@ -9458,12 +9509,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>228070f6-c47f-4f7b-a6b0-76d8abe818f3</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>453a6061-7c9d-4d99-a5a9-8b963c8c846d</t>
         </is>
@@ -9560,17 +9611,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>c6902a2f-fe58-4489-baf6-20e02a7ecb01</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>c79e62a9-b2b5-417d-a013-a0dbefa5bfd4</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>228070f6-c47f-4f7b-a6b0-76d8abe818f3</t>
         </is>
@@ -9627,12 +9678,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>cc68a12e-0e8a-42a9-bfd6-5f7c9687cf3f</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>6053fba2-dfd8-4f56-b15b-a3c1c488ecc0</t>
         </is>
@@ -9641,22 +9692,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4 [~5]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4 [~5]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Juggle Mistrust [Tag]</t>
+          <t>Juggle Mistrust</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Juggle Mistrust [Tag]</t>
+          <t>Juggle Mistrust</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9736,10 +9787,15 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
           <t>24ef26f6-00ec-47ed-889c-69992f4e72c7</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>5ebba108-f22a-4c3b-a3ec-6d5a528427b3</t>
         </is>
@@ -9796,12 +9852,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>07193dd0-f923-4b9e-bcdf-cfe43c6d0073</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>e5b6da5d-b3af-4179-8d6b-8e6204f756df</t>
         </is>
@@ -9858,12 +9914,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>087533d3-7b32-4028-9903-882f53af94af</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>e1e4f79f-e3d1-46f5-b04d-4ffffd718e39</t>
         </is>
@@ -9995,20 +10051,25 @@
       </c>
       <c r="X117" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y117" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y117" s="1" t="inlineStr">
+      <c r="Z117" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z117" s="1" t="inlineStr">
+      <c r="AA117" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA117" s="1" t="inlineStr">
+      <c r="AB117" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10025,12 +10086,12 @@
           <t>Moves starting from Art of Phoenix only - AOP</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>d0d46428-c4a7-4d18-9f37-5ea60725fffe</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>0234698e-52aa-498c-b2c4-ef87fa8dc9ef</t>
         </is>
@@ -10082,12 +10143,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>8b15273f-5f2b-4cdd-b372-a139740596d7</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>34f4bdbd-103e-4046-ba2a-bd5980a57e52</t>
         </is>
@@ -10184,12 +10245,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>003c8781-29d8-4d26-bf44-4e2cefd2c2da</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>cda84b7f-2644-4827-aa86-f03b254f7851</t>
         </is>
@@ -10281,12 +10342,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>1beba94c-235e-4b33-a3d1-b33d99c0793d</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>be6a3968-d8f0-4a1a-b370-c35a107e1fc0</t>
         </is>
@@ -10295,22 +10356,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>~1+2 [~5]</t>
+          <t>~1+2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>~1+2 [~5]</t>
+          <t>~1+2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Quick Wave Crest - [Tag]</t>
+          <t>Quick Wave Crest -</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Quick Wave Crest - [Tag]</t>
+          <t>Quick Wave Crest -</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10385,10 +10446,15 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
           <t>b29ebb4f-71c3-46ff-a564-c0665f8ce29a</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>411036bf-7019-4530-86c9-9e8210bb915a</t>
         </is>
@@ -10397,22 +10463,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>d+1+2 [~5]</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>d+1+2 [~5]</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Heavy Wave Crest - [Tag]</t>
+          <t>Heavy Wave Crest -</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Heavy Wave Crest - [Tag]</t>
+          <t>Heavy Wave Crest -</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10487,10 +10553,15 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
           <t>8e78110f-4b67-4ae2-b09e-28d0f56ba1af</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>f8f8275e-9d8a-4076-a6c8-038a0fdaf8fb</t>
         </is>
@@ -10499,22 +10570,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1+2 [~5]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1+2 [~5]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Power Wave Crest - [Tag]</t>
+          <t>Power Wave Crest -</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Power Wave Crest - [Tag]</t>
+          <t>Power Wave Crest -</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10589,10 +10660,15 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
           <t>3a25fb5f-d393-470f-b5d2-7c493209f04b</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>7c126533-6eef-48ee-9863-c4730809a72a</t>
         </is>
@@ -10649,12 +10725,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>c5b8ea02-4707-499c-be21-67ea8611cd84</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>a9b6f321-685b-4561-b08e-60109cd7cf45</t>
         </is>
@@ -10751,12 +10827,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>474c2981-1853-4472-ac5b-4f84dcabe5cb</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>735ac30b-4005-4ec2-ba93-899bfa69dce6</t>
         </is>
@@ -10818,12 +10894,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>580488b1-c279-4f84-8bd0-54174c845400</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>93efb4e9-751c-41ba-9b75-1a89423ae246</t>
         </is>
@@ -10920,12 +10996,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>434d7516-7ca3-4d2b-a419-c5707d1259cb</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>ebbaa062-52f7-4b7a-b7a6-1d78260b9385</t>
         </is>
@@ -11022,12 +11098,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>062c9f96-61a5-4f97-bdb3-64ab4c85395a</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>25e847da-7d68-4b0d-9121-e5320dded288</t>
         </is>
@@ -11129,12 +11205,12 @@
           <t>JG RC</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>b9ac8d5c-3cf5-47f5-b133-0e9dbc800ab0</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>671b59e4-956d-4b68-b2da-29229743c199</t>
         </is>
@@ -11236,12 +11312,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>360f8c33-8f4c-472d-b48b-afb45aa2824a</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>5eb1e44b-2bc2-4127-9f20-8729e9de6e3f</t>
         </is>
@@ -11293,12 +11369,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="Y132" t="inlineStr">
         <is>
           <t>987a1676-d0c0-438a-8e69-8ce9ec35af7f</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>5c053e58-fff3-49f3-a06a-8605548e8675</t>
         </is>
@@ -11390,12 +11466,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="Y133" t="inlineStr">
         <is>
           <t>fea0d91f-39e3-4926-a9ed-3bc833370e79</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>26a956ee-8ce8-41f0-baad-ab1a0c615698</t>
         </is>
@@ -11477,12 +11553,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>eba52a6a-4354-422e-bcd5-c23c11453761</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>a21db126-2f0b-44b8-ab96-9549740a1cad</t>
         </is>
@@ -11539,12 +11615,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
+      <c r="Y135" t="inlineStr">
         <is>
           <t>e8b6d600-c44b-4d97-a4b9-6d2ed3d201a9</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>79da43f9-f15c-401c-be49-caf21a5e722f</t>
         </is>
@@ -11641,12 +11717,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
+      <c r="Y136" t="inlineStr">
         <is>
           <t>c38c4db9-3d0c-46ec-91af-0cd4508ee5cd</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Z136" t="inlineStr">
         <is>
           <t>aa27bb14-ccf7-47c5-aa90-dcf490be8022</t>
         </is>
@@ -11743,12 +11819,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X137" t="inlineStr">
+      <c r="Y137" t="inlineStr">
         <is>
           <t>8fa918ec-1f5e-4f20-8e03-75328b81eaf2</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Z137" t="inlineStr">
         <is>
           <t>cb4812ee-6be2-484c-9112-114329bbd26d</t>
         </is>
@@ -11845,12 +11921,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
+      <c r="Y138" t="inlineStr">
         <is>
           <t>2a342267-1fd0-44f8-8e57-187e4ece4da1</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>b0b147bc-05ce-41c1-8fd6-987028a6dfb4</t>
         </is>
@@ -11952,12 +12028,12 @@
           <t>Input d+1+2 after the first kick to put ling back into AOP.</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>4016de06-dd0b-4e13-a819-95c550e4176c</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>529abc67-6bea-4927-9113-dabede12c8af</t>
         </is>
@@ -12054,12 +12130,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr">
+      <c r="Y140" t="inlineStr">
         <is>
           <t>9023ae52-908d-4bd7-8658-dbf302ba9bac</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>5a5ef6ea-0bcb-47b5-8754-1fb0fa1ef756</t>
         </is>
@@ -12191,20 +12267,25 @@
       </c>
       <c r="X143" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y143" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y143" s="1" t="inlineStr">
+      <c r="Z143" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z143" s="1" t="inlineStr">
+      <c r="AA143" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA143" s="1" t="inlineStr">
+      <c r="AB143" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -12291,12 +12372,12 @@
           <t>Damage increases to 50 then 80 as you Hypnotist Walk longer.</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="Y144" t="inlineStr">
         <is>
           <t>25f9b418-8f7d-4dca-b2a8-04c676fbd4aa</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Z144" t="inlineStr">
         <is>
           <t>d3a225ab-b800-42d6-9487-98fb5a037e09</t>
         </is>
@@ -12368,17 +12449,17 @@
           <t>[!]-</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="Y145" t="inlineStr">
         <is>
           <t>26909f52-7512-44a5-9bc0-0b5669dd6609</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Z145" t="inlineStr">
         <is>
           <t>ee40cdb8-7235-4abd-89c4-ab82725d3223</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
         <is>
           <t>25f9b418-8f7d-4dca-b2a8-04c676fbd4aa</t>
         </is>
@@ -12510,20 +12591,25 @@
       </c>
       <c r="X148" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y148" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y148" s="1" t="inlineStr">
+      <c r="Z148" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z148" s="1" t="inlineStr">
+      <c r="AA148" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA148" s="1" t="inlineStr">
+      <c r="AB148" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -12565,12 +12651,12 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
+      <c r="AB149" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12612,12 +12698,12 @@
           <t>mhhLLmmllmm</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Z150" t="inlineStr">
         <is>
           <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
+      <c r="AB150" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/ling_step7.xlsx
+++ b/sources/ling_step7.xlsx
@@ -425,7 +425,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -11383,22 +11383,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>(~B)RDS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11480,22 +11485,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>(~U)Quick roll to background; (~D)Quick roll to foreground</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12359,12 +12369,12 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -12446,7 +12456,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">

--- a/sources/ling_step7.xlsx
+++ b/sources/ling_step7.xlsx
@@ -1087,6 +1087,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -1154,6 +1159,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -1216,6 +1226,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1276,6 +1291,11 @@
       <c r="U12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -12661,6 +12681,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -12706,6 +12731,11 @@
       <c r="S150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
